--- a/site/exportExcel/lda.xlsx
+++ b/site/exportExcel/lda.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02912622876465321</v>
+        <v>0.03092783130705357</v>
       </c>
     </row>
     <row r="3">
@@ -464,11 +464,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>get</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.02912622876465321</v>
+        <v>0.03092782199382782</v>
       </c>
     </row>
     <row r="4">
@@ -477,11 +477,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02912622876465321</v>
+        <v>0.03092781081795692</v>
       </c>
     </row>
     <row r="5">
@@ -490,11 +490,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02912622876465321</v>
+        <v>0.03092780336737633</v>
       </c>
     </row>
     <row r="6">
@@ -503,11 +503,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>say</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02912622876465321</v>
+        <v>0.03092772699892521</v>
       </c>
     </row>
     <row r="7">
@@ -516,11 +516,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>become</t>
+          <t>lose</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01941747218370438</v>
+        <v>0.02061858773231506</v>
       </c>
     </row>
     <row r="8">
@@ -529,11 +529,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01941747218370438</v>
+        <v>0.02061858400702477</v>
       </c>
     </row>
     <row r="9">
@@ -542,11 +542,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bother</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01941747218370438</v>
+        <v>0.02061858400702477</v>
       </c>
     </row>
     <row r="10">
@@ -555,11 +555,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>deficit</t>
+          <t>vip</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01941747218370438</v>
+        <v>0.02061858214437962</v>
       </c>
     </row>
     <row r="11">
@@ -568,11 +568,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>adhd</t>
+          <t>part</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01941747218370438</v>
+        <v>0.02061857841908932</v>
       </c>
     </row>
   </sheetData>

--- a/site/exportExcel/lda.xlsx
+++ b/site/exportExcel/lda.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.03092783130705357</v>
+        <v>0.02845510095357895</v>
       </c>
     </row>
     <row r="3">
@@ -464,11 +464,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03092782199382782</v>
+        <v>0.02439012378454208</v>
       </c>
     </row>
     <row r="4">
@@ -477,11 +477,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03092781081795692</v>
+        <v>0.01626013778150082</v>
       </c>
     </row>
     <row r="5">
@@ -490,11 +490,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03092780336737633</v>
+        <v>0.0162600502371788</v>
       </c>
     </row>
     <row r="6">
@@ -503,11 +503,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03092772699892521</v>
+        <v>0.01626003719866276</v>
       </c>
     </row>
     <row r="7">
@@ -516,11 +516,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02061858773231506</v>
+        <v>0.01219512242823839</v>
       </c>
     </row>
     <row r="8">
@@ -529,11 +529,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02061858400702477</v>
+        <v>0.01219509728252888</v>
       </c>
     </row>
     <row r="9">
@@ -542,11 +542,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02061858400702477</v>
+        <v>0.01219509355723858</v>
       </c>
     </row>
     <row r="10">
@@ -555,11 +555,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02061858214437962</v>
+        <v>0.01219509355723858</v>
       </c>
     </row>
     <row r="11">
@@ -568,11 +568,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02061857841908932</v>
+        <v>0.012195092625916</v>
       </c>
     </row>
   </sheetData>
